--- a/odk/source/crop_sown_registry_sown.xlsx
+++ b/odk/source/crop_sown_registry_sown.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N213"/>
+  <dimension ref="A1:O213"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.48046875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="29" min="1" max="1"/>
@@ -610,6 +610,11 @@
           <t>repeat_count</t>
         </is>
       </c>
+      <c r="O1" s="29" t="inlineStr">
+        <is>
+          <t>required_message</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customFormat="1" customHeight="1" s="29">
       <c r="A2" s="33" t="inlineStr">
@@ -685,6 +690,11 @@
       <c r="L3" s="35" t="n"/>
       <c r="M3" s="35" t="n"/>
       <c r="N3" s="29" t="n"/>
+      <c r="O3" s="29" t="inlineStr">
+        <is>
+          <t>Enter the Fayda ID (FAN).</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customFormat="1" customHeight="1" s="29">
       <c r="A4" s="35" t="inlineStr">
@@ -724,6 +734,11 @@
       <c r="K4" s="35" t="n"/>
       <c r="L4" s="35" t="n"/>
       <c r="M4" s="35" t="n"/>
+      <c r="O4" s="29" t="inlineStr">
+        <is>
+          <t>Enter the crop year.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customFormat="1" customHeight="1" s="29">
       <c r="A5" s="35" t="inlineStr">
@@ -755,6 +770,11 @@
       <c r="K5" s="35" t="n"/>
       <c r="L5" s="35" t="n"/>
       <c r="M5" s="35" t="n"/>
+      <c r="O5" s="29" t="inlineStr">
+        <is>
+          <t>Select the production season.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customFormat="1" customHeight="1" s="39">
       <c r="A6" s="33" t="inlineStr">
@@ -823,6 +843,11 @@
         </is>
       </c>
       <c r="G8" s="36" t="n"/>
+      <c r="O8" s="29" t="inlineStr">
+        <is>
+          <t>Enter the Land ID.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="34">
       <c r="A9" s="35" t="inlineStr">
@@ -837,7 +862,7 @@
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>Cluster / Non Cluster Status</t>
+          <t>Cluster Status</t>
         </is>
       </c>
       <c r="D9" s="35" t="n"/>
@@ -905,7 +930,7 @@
       </c>
       <c r="C11" s="41" t="inlineStr">
         <is>
-          <t>FPC Name</t>
+          <t>Farmer Production Cluster (FPC) Name</t>
         </is>
       </c>
       <c r="D11" s="35" t="n"/>
@@ -1052,7 +1077,7 @@
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
-          <t>Area Sown (ha) (Cluster)</t>
+          <t>Area Sown (ha)</t>
         </is>
       </c>
       <c r="D16" s="35" t="n"/>
@@ -1254,6 +1279,11 @@
       </c>
       <c r="L22" s="35" t="n"/>
       <c r="M22" s="36" t="n"/>
+      <c r="O22" s="29" t="inlineStr">
+        <is>
+          <t>Select the actual crop name.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customFormat="1" customHeight="1" s="29">
       <c r="A23" s="35" t="inlineStr">
@@ -1268,7 +1298,7 @@
       </c>
       <c r="C23" s="35" t="inlineStr">
         <is>
-          <t>Sowing Date (GC)</t>
+          <t>Sowing Date (Gregorian calendar)</t>
         </is>
       </c>
       <c r="D23" s="35" t="n"/>
@@ -1343,7 +1373,11 @@
           <t>. &gt;= 0</t>
         </is>
       </c>
-      <c r="G25" s="35" t="n"/>
+      <c r="G25" s="35" t="inlineStr">
+        <is>
+          <t>Actual Fertilizer Quantity cannot be negative.</t>
+        </is>
+      </c>
       <c r="H25" s="36" t="n"/>
       <c r="I25" s="35" t="n"/>
       <c r="J25" s="35" t="n"/>
@@ -1409,7 +1443,7 @@
       </c>
       <c r="C28" s="35" t="inlineStr">
         <is>
-          <t>DA Name</t>
+          <t>Development Agent Name</t>
         </is>
       </c>
       <c r="D28" s="35" t="n"/>
@@ -1421,7 +1455,7 @@
       </c>
       <c r="G28" s="35" t="inlineStr">
         <is>
-          <t>DA Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+          <t>Enter the Development Agent's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
       <c r="H28" s="35" t="n"/>
@@ -1443,12 +1477,12 @@
       </c>
       <c r="C29" s="35" t="inlineStr">
         <is>
-          <t>DA Mobile Number</t>
+          <t>Development Agent Mobile Number</t>
         </is>
       </c>
       <c r="D29" s="36" t="inlineStr">
         <is>
-          <t>Format: 0911223344 or +251911223344</t>
+          <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
       <c r="E29" s="35" t="n"/>
@@ -1459,7 +1493,7 @@
       </c>
       <c r="G29" s="36" t="inlineStr">
         <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
       <c r="H29" s="36" t="n"/>
@@ -1493,7 +1527,7 @@
       </c>
       <c r="G30" s="35" t="inlineStr">
         <is>
-          <t>Supervisor Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+          <t>Enter the supervisor's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
       <c r="H30" s="35" t="n"/>
@@ -1520,7 +1554,7 @@
       </c>
       <c r="D31" s="36" t="inlineStr">
         <is>
-          <t>Format: 0911223344 or +251911223344</t>
+          <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
       <c r="E31" s="35" t="n"/>
@@ -1531,7 +1565,7 @@
       </c>
       <c r="G31" s="36" t="inlineStr">
         <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
       <c r="H31" s="35" t="n"/>
@@ -1632,6 +1666,11 @@
           <t>Land ID does not match the Land ID provided in Sowing Details. Please enter the correct Land ID.</t>
         </is>
       </c>
+      <c r="O35" s="29" t="inlineStr">
+        <is>
+          <t>Enter the Land ID.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="34">
       <c r="A36" s="35" t="inlineStr">
@@ -1646,7 +1685,7 @@
       </c>
       <c r="C36" s="35" t="inlineStr">
         <is>
-          <t>Cluster / Non Cluster Status</t>
+          <t>Cluster Status</t>
         </is>
       </c>
       <c r="D36" s="35" t="n"/>
@@ -1678,7 +1717,7 @@
       </c>
       <c r="C37" s="35" t="inlineStr">
         <is>
-          <t>FPC Name</t>
+          <t>Farmer Production Cluster (FPC) Name</t>
         </is>
       </c>
       <c r="D37" s="35" t="n"/>
@@ -1735,6 +1774,11 @@
       </c>
       <c r="L38" s="35" t="n"/>
       <c r="M38" s="36" t="n"/>
+      <c r="O38" s="29" t="inlineStr">
+        <is>
+          <t>Select the crop type affected.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customFormat="1" customHeight="1" s="29">
       <c r="A39" s="35" t="inlineStr">
@@ -1811,7 +1855,7 @@
       </c>
       <c r="C41" s="35" t="inlineStr">
         <is>
-          <t>Date of Observation (GC)</t>
+          <t>Date of Observation (Gregorian calendar)</t>
         </is>
       </c>
       <c r="D41" s="35" t="n"/>
@@ -1846,7 +1890,7 @@
       </c>
       <c r="C42" s="38" t="inlineStr">
         <is>
-          <t>The selected date will be automatically converted to Ethiopian Calendar (EC) format.</t>
+          <t>The date you select is converted to the Ethiopian calendar automatically.</t>
         </is>
       </c>
       <c r="D42" s="35" t="n"/>
@@ -1900,10 +1944,14 @@
       </c>
       <c r="C44" s="37" t="inlineStr">
         <is>
-          <t>Estimated Crop Damage (%) or (ha)</t>
-        </is>
-      </c>
-      <c r="D44" s="35" t="n"/>
+          <t>Estimated Crop Damage (percent or hectares)</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>Write the amount followed by % or ha, for example 20% or 0.5 ha.</t>
+        </is>
+      </c>
       <c r="E44" s="35" t="n"/>
       <c r="F44" s="35" t="n"/>
       <c r="G44" s="35" t="n"/>
@@ -2297,7 +2345,7 @@
       </c>
       <c r="C58" s="40" t="inlineStr">
         <is>
-          <t>Weedicides Type</t>
+          <t>Weedicide Type</t>
         </is>
       </c>
       <c r="D58" s="40" t="n"/>
@@ -2329,7 +2377,7 @@
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
-          <t>Weedicides Name</t>
+          <t>Weedicide Name</t>
         </is>
       </c>
       <c r="D59" s="40" t="n"/>
@@ -5381,7 +5429,7 @@
       </c>
       <c r="C43" s="51" t="inlineStr">
         <is>
-          <t>Cultural (e.g. Liming, Crop Rotation)</t>
+          <t>Cultural (for example liming or crop rotation)</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6334,7 @@
       </c>
       <c r="C100" s="55" t="inlineStr">
         <is>
-          <t>Bio Fertilizer</t>
+          <t>Bio-fertilizer</t>
         </is>
       </c>
       <c r="D100" s="40" t="n"/>
@@ -7630,7 +7678,7 @@
       </c>
       <c r="C183" s="55" t="inlineStr">
         <is>
-          <t>Nps</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="D183" s="40" t="n"/>
@@ -7652,7 +7700,7 @@
       </c>
       <c r="C184" s="55" t="inlineStr">
         <is>
-          <t>Npsb</t>
+          <t>NPSB</t>
         </is>
       </c>
       <c r="D184" s="40" t="n"/>
@@ -7674,7 +7722,7 @@
       </c>
       <c r="C185" s="55" t="inlineStr">
         <is>
-          <t>Dap</t>
+          <t>DAP</t>
         </is>
       </c>
       <c r="D185" s="40" t="n"/>
@@ -8682,7 +8730,7 @@
     <row r="2" ht="15" customHeight="1" s="34">
       <c r="A2" s="29" t="inlineStr">
         <is>
-          <t>CSR – 3. Sowing</t>
+          <t>Crop Sown Registry - 3. Sowing</t>
         </is>
       </c>
       <c r="B2" s="29" t="inlineStr">
